--- a/data/performance/daily/signal_list_2026-06-05.xlsx
+++ b/data/performance/daily/signal_list_2026-06-05.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 33.3%  (2W / 4L of 6 evaluated)</t>
+          <t>Win Rate: 0.0%  (0W / 6L of 6 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>288</v>
+        <v>293.97</v>
       </c>
       <c r="D5" t="n">
         <v>288</v>
@@ -553,10 +553,10 @@
         <v>288</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>916.8200000000001</v>
+        <v>1090</v>
       </c>
       <c r="D6" t="n">
         <v>900</v>
@@ -595,10 +595,10 @@
         <v>916.8200000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>-15.89</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.83</v>
+        <v>-17.43</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D8" t="n">
         <v>498</v>
@@ -679,14 +679,14 @@
         <v>500</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.4</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" t="n">
         <v>107</v>
@@ -721,10 +721,10 @@
         <v>117</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.76</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D10" t="n">
         <v>101</v>
@@ -763,14 +763,14 @@
         <v>114</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>22.58</v>
+        <v>12.87</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 26.7%  (4W / 11L of 15 evaluated, 1 pending)</t>
+          <t>Win Rate: 20.0%  (3W / 12L of 15 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>288</v>
+        <v>293.97</v>
       </c>
       <c r="D5" t="n">
         <v>288</v>
@@ -897,10 +897,10 @@
         <v>288</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
         <v>64</v>
@@ -939,10 +939,10 @@
         <v>65</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>-2.99</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.54</v>
+        <v>-4.48</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6300</v>
+        <v>6225</v>
       </c>
       <c r="D7" t="n">
         <v>7450</v>
@@ -981,10 +981,10 @@
         <v>7450</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>18.25</v>
+        <v>19.68</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18.25</v>
+        <v>19.68</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="D8" t="n">
         <v>2020</v>
@@ -1023,10 +1023,10 @@
         <v>2020</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>24.31</v>
+        <v>24.69</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>24.31</v>
+        <v>24.69</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="D9" t="n">
         <v>865</v>
@@ -1065,10 +1065,10 @@
         <v>985</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-12.18</v>
+        <v>-13.07</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D11" t="n">
         <v>196</v>
@@ -1149,10 +1149,10 @@
         <v>234</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.63</v>
+        <v>1.74</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-14.04</v>
+        <v>-14.78</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1233,10 +1233,10 @@
         <v>141</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.3</v>
+        <v>-9.93</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D15" t="n">
         <v>280</v>
@@ -1307,10 +1307,10 @@
         <v>314</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>-3.09</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.83</v>
+        <v>-13.58</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" t="n">
         <v>107</v>
@@ -1391,10 +1391,10 @@
         <v>117</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-7.76</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D18" t="n">
         <v>101</v>
@@ -1433,14 +1433,14 @@
         <v>114</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>22.58</v>
+        <v>12.87</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1060</v>
+        <v>1030</v>
       </c>
       <c r="D19" t="n">
         <v>1000</v>
@@ -1475,10 +1475,10 @@
         <v>1065</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.47</v>
+        <v>3.4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.66</v>
+        <v>-2.91</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1825</v>
+        <v>1840</v>
       </c>
       <c r="D20" t="n">
         <v>1600</v>
@@ -1517,10 +1517,10 @@
         <v>1845</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.1</v>
+        <v>0.27</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-12.33</v>
+        <v>-13.04</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>

--- a/data/performance/daily/signal_list_2026-06-05.xlsx
+++ b/data/performance/daily/signal_list_2026-06-05.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-05.xlsx
+++ b/data/performance/daily/signal_list_2026-06-05.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-05.xlsx
+++ b/data/performance/daily/signal_list_2026-06-05.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -455,9 +455,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,7 +488,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -512,15 +513,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -544,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -554,9 +560,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,7 +593,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -611,15 +618,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -656,12 +668,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-05.xlsx
+++ b/data/performance/daily/signal_list_2026-06-05.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -453,12 +453,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,45 +489,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -550,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,12 +564,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -593,45 +600,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -652,33 +664,36 @@
         <v>655</v>
       </c>
       <c r="D5" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5" t="n">
         <v>750</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>785</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>19.85</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
